--- a/output/pdf_financials_xlsx/SHK.P.xlsx
+++ b/output/pdf_financials_xlsx/SHK.P.xlsx
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="93">
@@ -6163,7 +6163,11 @@
           <t>Share-based payments reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -6651,7 +6655,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -9614,10 +9622,10 @@
         </is>
       </c>
       <c r="K63" s="5" t="n">
-        <v>0.043592</v>
+        <v>-0.043592</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.028859</v>
+        <v>-0.028859</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -9677,10 +9685,10 @@
         </is>
       </c>
       <c r="K64" s="5" t="n">
-        <v>2e-08</v>
+        <v>-2e-08</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>1.4e-08</v>
+        <v>-1.4e-08</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SHK.P.xlsx
+++ b/output/pdf_financials_xlsx/SHK.P.xlsx
@@ -1939,22 +1939,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.100191</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.191904</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.173154</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.101238</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.020692</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
@@ -2011,22 +2011,22 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.100191</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.191904</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.173154</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.101238</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.020692</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6e-06</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">

--- a/output/pdf_financials_xlsx/SHK.P.xlsx
+++ b/output/pdf_financials_xlsx/SHK.P.xlsx
@@ -552,10 +552,8 @@
       <c r="I4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -600,10 +598,8 @@
       <c r="I5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -648,10 +644,8 @@
       <c r="I6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -694,12 +688,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.006935</v>
       </c>
     </row>
     <row r="8">
@@ -744,10 +736,8 @@
       <c r="I8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -792,10 +782,8 @@
       <c r="I9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -840,10 +828,8 @@
       <c r="I10" s="3" t="n">
         <v>0.013335</v>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J10" s="3" t="n">
+        <v>0.024221</v>
       </c>
     </row>
     <row r="11">
@@ -888,10 +874,8 @@
       <c r="I11" s="3" t="n">
         <v>-0.013335</v>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J11" s="3" t="n">
+        <v>-0.024221</v>
       </c>
     </row>
     <row r="12">
@@ -936,10 +920,8 @@
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -984,10 +966,8 @@
       <c r="I13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -1032,10 +1012,8 @@
       <c r="I14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1080,10 +1058,8 @@
       <c r="I15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1126,12 +1102,10 @@
         <v>-0.043592</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0.043592</v>
-      </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.2e-08</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>-4.6e-08</v>
       </c>
     </row>
     <row r="17">
@@ -1176,10 +1150,8 @@
       <c r="I17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1326,12 +1298,10 @@
         <v>-0.043592</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0.043592</v>
-      </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.2e-08</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>-4.6e-08</v>
       </c>
     </row>
     <row r="21">
@@ -1376,10 +1346,8 @@
       <c r="I21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1424,10 +1392,8 @@
       <c r="I22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1460,12 +1426,10 @@
         <v>-0.043592</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-0.043592</v>
-      </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.2e-08</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>-4.6e-08</v>
       </c>
     </row>
     <row r="24">
@@ -1664,12 +1628,10 @@
         <v>-0.043592</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.043592</v>
-      </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.2e-08</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>-4.6e-08</v>
       </c>
     </row>
     <row r="28">
@@ -1714,10 +1676,8 @@
       <c r="I28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1760,12 +1720,10 @@
         <v>-0.043592</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.043592</v>
-      </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.2e-08</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>-4.6e-08</v>
       </c>
     </row>
     <row r="30">
@@ -1862,10 +1820,8 @@
       <c r="I31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4404,10 +4360,8 @@
       <c r="I99" s="3" t="n">
         <v>-0.028859</v>
       </c>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J99" s="3" t="n">
+        <v>-4.6e-08</v>
       </c>
     </row>
     <row r="100">
@@ -4442,10 +4396,8 @@
       <c r="I100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -4480,10 +4432,8 @@
       <c r="I101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -4518,10 +4468,8 @@
       <c r="I102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -4556,10 +4504,8 @@
       <c r="I103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -4594,10 +4540,8 @@
       <c r="I104" s="3" t="n">
         <v>0.013853</v>
       </c>
-      <c r="J104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -4632,10 +4576,8 @@
       <c r="I105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -4670,10 +4612,8 @@
       <c r="I106" s="3" t="n">
         <v>0.013853</v>
       </c>
-      <c r="J106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J106" s="3" t="n">
+        <v>-0.02107</v>
       </c>
     </row>
     <row r="107">
@@ -4708,10 +4648,8 @@
       <c r="I107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J107" s="3" t="n">
+        <v>0.0187</v>
       </c>
     </row>
     <row r="108">
@@ -4746,10 +4684,8 @@
       <c r="I108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -4784,10 +4720,8 @@
       <c r="I109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -4822,10 +4756,8 @@
       <c r="I110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -4860,10 +4792,8 @@
       <c r="I111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -4898,10 +4828,8 @@
       <c r="I112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -4936,10 +4864,8 @@
       <c r="I113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -4974,10 +4900,8 @@
       <c r="I114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -5012,10 +4936,8 @@
       <c r="I115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5050,10 +4972,8 @@
       <c r="I116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5088,10 +5008,8 @@
       <c r="I117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5126,10 +5044,8 @@
       <c r="I118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5169,15 +5085,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5212,10 +5124,8 @@
       <c r="I120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J120" s="3" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="121">
@@ -5250,10 +5160,8 @@
       <c r="I121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -5288,10 +5196,8 @@
       <c r="I122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -5326,10 +5232,8 @@
       <c r="I123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -5364,10 +5268,8 @@
       <c r="I124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5402,10 +5304,8 @@
       <c r="I125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5440,10 +5340,8 @@
       <c r="I126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -5530,10 +5428,8 @@
       <c r="I128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J128" s="3" t="n">
+        <v>-0.006241</v>
       </c>
     </row>
     <row r="129">
@@ -5573,15 +5469,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>0.193759</v>
       </c>
     </row>
     <row r="130">
@@ -5616,10 +5508,8 @@
       <c r="I130" s="3" t="n">
         <v>6e-06</v>
       </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J130" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5654,10 +5544,8 @@
       <c r="I131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -5692,10 +5580,8 @@
       <c r="I132" s="3" t="n">
         <v>-6e-06</v>
       </c>
-      <c r="J132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J132" s="3" t="n">
+        <v>0.124549</v>
       </c>
     </row>
     <row r="133">
@@ -5730,10 +5616,8 @@
       <c r="I133" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J133" s="3" t="n">
+        <v>0.124549</v>
       </c>
     </row>
     <row r="134">
@@ -5768,10 +5652,8 @@
       <c r="I134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -5806,10 +5688,8 @@
       <c r="I135" s="3" t="n">
         <v>-0.015006</v>
       </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J135" s="3" t="n">
+        <v>-0.06920999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5823,7 +5703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7923,17 +7803,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Changes in non-cash working capital items total</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -7966,16 +7846,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K36" s="5" t="n">
-        <v>-0.043592</v>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.028859</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013853</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>-0.02107</v>
       </c>
     </row>
     <row r="37">
@@ -7986,17 +7866,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Share based compensation</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -8029,16 +7909,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K37" s="5" t="n">
-        <v>0.022906</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>0.013853</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0.0187</v>
       </c>
     </row>
     <row r="38">
@@ -8049,7 +7931,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8092,16 +7974,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K38" s="5" t="n">
-        <v>-0.020686</v>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L38" s="5" t="n">
         <v>-0.015006</v>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M38" s="5" t="n">
+        <v>-0.06920999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -8112,12 +7994,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Note payable (Note 11)</t>
+          <t>Notes payable (note 11)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -8151,8 +8033,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K39" s="5" t="n">
-        <v>0</v>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L39" s="5" t="n">
         <v>0.015</v>
@@ -8171,17 +8055,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
+          <t>Proceeds on issuance of capital stock (note 5)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>IssuanceOfCapitalStock</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -8214,16 +8098,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K40" s="5" t="n">
-        <v>-0.020686</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>-6e-06</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="41">
@@ -8234,17 +8120,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Share issuance costs</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -8257,11 +8143,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n">
-        <v>0.100191</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>0.191904</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -8273,16 +8163,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K41" s="5" t="n">
-        <v>0.020692</v>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>6e-06</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>-0.006241</v>
       </c>
     </row>
     <row r="42">
@@ -8293,17 +8185,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Cash provided by financing activities</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -8316,11 +8208,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G42" s="5" t="n">
-        <v>0.191904</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>0.173154</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -8332,16 +8228,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K42" s="5" t="n">
-        <v>6e-06</v>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.015</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>0.193759</v>
       </c>
     </row>
     <row r="43">
@@ -8352,17 +8248,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Net change in cash</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -8390,21 +8286,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J43" s="5" t="n">
-        <v>-0.080293</v>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>-0.043592</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>-6e-06</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>0.124549</v>
       </c>
     </row>
     <row r="44">
@@ -8415,15 +8311,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Accounts payable and accruals</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -8434,30 +8334,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n">
-        <v>0.005228</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>0.002484</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>0.004165</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>-0.000253</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>0.022906</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -8468,17 +8374,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
+          <t>Cash, end of year</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -8486,33 +8392,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>0.000191</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>-0.057966</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>-0.01875</v>
-      </c>
-      <c r="I45" s="5" t="n">
-        <v>-0.07191599999999999</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>-0.08054600000000001</v>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>-0.020686</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0.124549</v>
       </c>
     </row>
     <row r="46">
@@ -8523,17 +8437,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Net change in cash during the year</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -8551,22 +8465,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H46" s="5" t="n">
-        <v>-0.01875</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>-0.07191599999999999</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>-0.08054600000000001</v>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.020686</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.043592</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>-0.028859</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -8582,17 +8500,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -8610,22 +8528,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H47" s="5" t="n">
-        <v>0.191904</v>
-      </c>
-      <c r="I47" s="5" t="n">
-        <v>0.173154</v>
-      </c>
-      <c r="J47" s="5" t="n">
-        <v>0.101238</v>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0.020692</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022906</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0.013853</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -8641,17 +8563,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -8669,22 +8591,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>0.173154</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>0.101238</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>0.020692</v>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>6e-06</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.020686</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>-0.015006</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -8700,19 +8626,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Net (loss) income for the year $</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Note payable (Note 11)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -8723,27 +8645,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.093017</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>-0.021234</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>-0.076081</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>-0.080293</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>0.015</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -8759,17 +8685,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
+          <t>Net change in cash</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -8782,8 +8708,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G50" s="5" t="n">
-        <v>0.029823</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -8800,15 +8728,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K50" s="5" t="n">
+        <v>-0.020686</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-6e-06</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -8824,28 +8748,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Items not affecting cash total</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>0.000191</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.063194</v>
+        <v>0.100191</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>-0.021234</v>
+        <v>0.191904</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -8857,15 +8787,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K51" s="5" t="n">
+        <v>0.020692</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>6e-06</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -8886,12 +8812,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Issuance of capital stock (Note 5)</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IssuanceOfCapitalStock</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -8899,16 +8825,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>0.1</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.191904</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0.173154</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -8920,15 +8846,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K52" s="5" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -8944,17 +8866,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8967,8 +8889,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.050321</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -8980,15 +8904,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J53" s="5" t="n">
+        <v>-0.080293</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>-0.043592</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -9009,49 +8929,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Financing Activity total</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Accounts payable and accruals</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F54" s="5" t="n">
-        <v>0.1</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.149679</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005228</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0.002484</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0.004165</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>-0.000253</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0.022906</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -9072,17 +8982,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Net change in cash during the year</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -9090,31 +9000,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F55" s="5" t="n">
+        <v>0.000191</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.091713</v>
+        <v>-0.057966</v>
       </c>
       <c r="H55" s="5" t="n">
         <v>-0.01875</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="5" t="n">
+        <v>-0.07191599999999999</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>-0.08054600000000001</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>-0.020686</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -9135,17 +9037,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Net (loss) income for the period $</t>
+          <t>Net change in cash during the year</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9153,31 +9055,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F56" s="5" t="n">
-        <v>0.000191</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.093017</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>-0.01875</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>-0.07191599999999999</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>-0.08054600000000001</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>-0.020686</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -9198,17 +9096,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Net change in cash during the period</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -9216,31 +9114,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>0.100191</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.091713</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0.191904</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.173154</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0.101238</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.020692</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -9261,17 +9155,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -9284,28 +9178,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n">
-        <v>0.100191</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0.173154</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.101238</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0.020692</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>6e-06</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -9326,17 +9214,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
+          <t>Net (loss) income for the year $</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -9344,26 +9232,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F59" s="5" t="n">
-        <v>0.100191</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.191904</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.093017</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>-0.021234</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>-0.076081</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>-0.080293</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -9384,22 +9268,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Professional fees $</t>
+          <t>Stock based compensation</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -9412,10 +9296,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G60" s="5" t="n">
+        <v>0.029823</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -9432,11 +9314,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K60" s="5" t="n">
-        <v>0.033081</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>0.014038</v>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -9447,43 +9333,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Items not affecting cash total</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F61" s="5" t="n">
+        <v>0.000191</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>-0.063194</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>-0.021234</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -9495,11 +9371,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K61" s="5" t="n">
-        <v>0.010511</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>0.013335</v>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -9510,22 +9390,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Issuance of capital stock (Note 5)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>IssuanceOfCapitalStock</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -9533,15 +9413,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F62" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.2</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -9558,11 +9434,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>0.001486</v>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -9573,22 +9453,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Net and Comprehensive Loss $</t>
+          <t>Share issuance costs</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -9601,10 +9481,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G63" s="5" t="n">
+        <v>-0.050321</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -9621,11 +9499,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K63" s="5" t="n">
-        <v>-0.043592</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>-0.028859</v>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -9636,22 +9518,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Loss per Share</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Basic and diluted loss for the period $</t>
+          <t>Financing Activity total</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -9659,15 +9541,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F64" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.149679</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -9684,11 +9562,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K64" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>-1.4e-08</v>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -9699,20 +9581,24 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>(Note 5)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Net change in cash during the year</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -9723,15 +9609,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G65" s="5" t="n">
+        <v>0.091713</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>-0.01875</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -9743,11 +9625,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K65" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>2</v>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -9758,34 +9644,34 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shares     Amount       Reserve       Deficit         Total</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2023 4,000,000 $ 239,118 $ 29,823 $</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Net (loss) income for the period $</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" s="5" t="n">
+        <v>0.000191</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>-0.093017</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -9802,11 +9688,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K66" s="5" t="n">
-        <v>0.009068</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>-0.259873</v>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -9817,22 +9707,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shares     Amount       Reserve       Deficit         Total</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Net loss for the year 0 0 0</t>
+          <t>Net change in cash during the period</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -9840,15 +9730,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F67" s="5" t="n">
+        <v>0.100191</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.091713</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -9865,11 +9751,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K67" s="5" t="n">
-        <v>-0.043592</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>-0.043592</v>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -9880,20 +9770,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shares     Amount       Reserve       Deficit         Total</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2024 4,000,000 $ 239,118 $ 29,823 $</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -9904,10 +9798,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G68" s="5" t="n">
+        <v>0.100191</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -9924,11 +9816,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K68" s="5" t="n">
-        <v>-0.034524</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>-0.303465</v>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -9939,34 +9835,34 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Expiry of employee stock</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Expiry of employee stock options 0 0 (29,823)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Cash, end of period $</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F69" s="5" t="n">
+        <v>0.100191</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.191904</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -9983,11 +9879,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>0.029823</v>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -10003,19 +9903,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expiry of employee stock</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Net loss for the year 0 0 0</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Audit and accounting fees $</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -10046,16 +9942,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K70" s="5" t="n">
-        <v>-0.028859</v>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.028859</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012013</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>0.014237</v>
       </c>
     </row>
     <row r="71">
@@ -10066,52 +9962,1034 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Legal fees</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>0.002025</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>0.006935</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>0.010511</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>0.013335</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0.024221</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Share based compensation</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>0.0187</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Interest on note payable</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>0.001486</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>0.002747</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>-0.028859</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>-0.06684</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Loss per Share</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss for the period $</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>-7.2e-08</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>-4.6e-08</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding (Note 5)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>1.441319</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>0.033081</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>0.014038</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>0.001486</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Net and Comprehensive Loss $</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>-0.043592</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>-0.028859</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>(Note 5)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Shares     Amount       Reserve       Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2023 4,000,000 $ 239,118 $ 29,823 $</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>0.009068</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>-0.259873</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Shares     Amount       Reserve       Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Net loss for the year 0 0 0</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>-0.043592</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>-0.043592</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Shares     Amount       Reserve       Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2024 4,000,000 $ 239,118 $ 29,823 $</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>-0.034524</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>-0.303465</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>Expiry of employee stock</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Expiry of employee stock options 0 0 (29,823)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>0.029823</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Expiry of employee stock</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Net loss for the year 0 0 0</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>-0.028859</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>-0.028859</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Expiry of employee stock</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>Balance, March 31, 2025 4,000,000 $ 239,118 $ 0 $</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K71" s="5" t="n">
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
         <v>-0.06338299999999999</v>
       </c>
-      <c r="L71" s="5" t="n">
+      <c r="L87" s="5" t="n">
         <v>-0.302501</v>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
